--- a/backtest_runs/20260410_193731/by_symbol/EPQL/EPQL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/EPQL/EPQL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>102179.44</v>
@@ -771,7 +771,7 @@
         <v>-686.1199999999925</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>104116.72</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>104116.72</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>104116.72</v>
@@ -1001,7 +1001,7 @@
         <v>-3349.879999999993</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>101372.24</v>
@@ -1093,7 +1093,7 @@
         <v>-282.5200000000011</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>101654.76</v>
@@ -1185,7 +1185,7 @@
         <v>-726.4799999999989</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>101291.52</v>
@@ -1231,7 +1231,7 @@
         <v>-80.71999999999828</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>101210.8</v>
@@ -1277,7 +1277,7 @@
         <v>-2098.720000000013</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>99112.08</v>
@@ -1415,7 +1415,7 @@
         <v>-887.9199999999954</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100363.24</v>
@@ -1507,7 +1507,7 @@
         <v>-605.3999999999943</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>102179.44</v>
@@ -1553,7 +1553,7 @@
         <v>-968.6399999999937</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>101210.8</v>
@@ -1645,7 +1645,7 @@
         <v>-1856.560000000003</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>103188.44</v>
